--- a/TT_fomat (4).xlsx
+++ b/TT_fomat (4).xlsx
@@ -1,21 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vaibhav Rathod\Desktop\tt\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D001346B-2F2F-4C9F-8D6B-5E830DEA5043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="BASE SHEET" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="ROOM DETAILS" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="MDM COURSES" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="FACULTY NA" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Sheet5" sheetId="5" r:id="rId9"/>
+    <sheet name="BASE SHEET" sheetId="1" r:id="rId1"/>
+    <sheet name="ROOM DETAILS" sheetId="2" r:id="rId2"/>
+    <sheet name="MDM COURSES" sheetId="3" r:id="rId3"/>
+    <sheet name="FACULTY NA" sheetId="4" r:id="rId4"/>
+    <sheet name="ROOM_NA" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="194">
   <si>
     <t>CLASS</t>
   </si>
@@ -551,9 +560,6 @@
     <t>B417A</t>
   </si>
   <si>
-    <t>LAB</t>
-  </si>
-  <si>
     <t>B414</t>
   </si>
   <si>
@@ -585,45 +591,69 @@
   </si>
   <si>
     <t xml:space="preserve">     </t>
+  </si>
+  <si>
+    <t>LAB_H</t>
+  </si>
+  <si>
+    <t>LAB_S</t>
+  </si>
+  <si>
+    <t>ROOM_NO</t>
+  </si>
+  <si>
+    <t>FIXED_CLASS</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d-m"/>
+    <numFmt numFmtId="164" formatCode="d\-m"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
@@ -633,7 +663,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -667,27 +697,39 @@
     </fill>
   </fills>
   <borders count="5">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -697,6 +739,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -711,107 +754,62 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1001,25 +999,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AB100"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="6" max="6" width="16.38"/>
-    <col customWidth="1" min="7" max="7" width="17.13"/>
-    <col customWidth="1" min="8" max="8" width="17.0"/>
-    <col customWidth="1" min="9" max="9" width="22.0"/>
-    <col customWidth="1" min="10" max="10" width="11.0"/>
-    <col customWidth="1" min="11" max="11" width="10.13"/>
+    <col min="6" max="6" width="16.33203125" customWidth="1"/>
+    <col min="7" max="7" width="17.109375" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1044,38 +1045,41 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-    </row>
-    <row r="2">
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+    </row>
+    <row r="2" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>12</v>
@@ -1099,18 +1103,21 @@
         <v>18</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="L2" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>12</v>
@@ -1119,7 +1126,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>15</v>
@@ -1134,18 +1141,21 @@
         <v>21</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="2">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>12</v>
@@ -1169,18 +1179,21 @@
         <v>18</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="L4" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>12</v>
@@ -1189,7 +1202,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>15</v>
@@ -1204,18 +1217,21 @@
         <v>26</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="L5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>12</v>
@@ -1239,18 +1255,21 @@
         <v>18</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="L6" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>12</v>
@@ -1259,7 +1278,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>15</v>
@@ -1274,18 +1293,21 @@
         <v>31</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="L7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>12</v>
@@ -1309,18 +1331,21 @@
         <v>18</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="L8" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>12</v>
@@ -1329,7 +1354,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>15</v>
@@ -1343,19 +1368,22 @@
       <c r="I9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="2">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>12</v>
@@ -1379,18 +1407,21 @@
         <v>18</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="2">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="L10" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>12</v>
@@ -1399,7 +1430,7 @@
         <v>13</v>
       </c>
       <c r="E11" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>15</v>
@@ -1414,18 +1445,21 @@
         <v>38</v>
       </c>
       <c r="J11" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K11" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="L11" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>12</v>
@@ -1434,7 +1468,7 @@
         <v>13</v>
       </c>
       <c r="E12" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>15</v>
@@ -1449,18 +1483,21 @@
         <v>41</v>
       </c>
       <c r="J12" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="2">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="L12" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>42</v>
@@ -1484,18 +1521,21 @@
         <v>45</v>
       </c>
       <c r="J13" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="L13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>42</v>
@@ -1519,18 +1559,21 @@
         <v>21</v>
       </c>
       <c r="J14" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K14" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="L14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>42</v>
@@ -1539,7 +1582,7 @@
         <v>13</v>
       </c>
       <c r="E15" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>15</v>
@@ -1553,19 +1596,20 @@
       <c r="I15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" s="2"/>
+      <c r="K15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="L15" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>42</v>
@@ -1574,7 +1618,7 @@
         <v>13</v>
       </c>
       <c r="E16" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>15</v>
@@ -1588,19 +1632,20 @@
       <c r="I16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="2"/>
+      <c r="K16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K16" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="L16" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>42</v>
@@ -1623,19 +1668,20 @@
       <c r="I17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="2"/>
+      <c r="K17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="L17" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B18" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>42</v>
@@ -1644,7 +1690,7 @@
         <v>13</v>
       </c>
       <c r="E18" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>15</v>
@@ -1658,19 +1704,20 @@
       <c r="I18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="2"/>
+      <c r="K18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K18" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="L18" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -1693,19 +1740,20 @@
       <c r="I19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="2"/>
+      <c r="K19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K19" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="L19" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B20" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>42</v>
@@ -1728,19 +1776,20 @@
       <c r="I20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="2"/>
+      <c r="K20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K20" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="L20" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B21" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>42</v>
@@ -1749,7 +1798,7 @@
         <v>13</v>
       </c>
       <c r="E21" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>15</v>
@@ -1763,19 +1812,20 @@
       <c r="I21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="2"/>
+      <c r="K21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K21" s="2">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="L21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>42</v>
@@ -1784,7 +1834,7 @@
         <v>13</v>
       </c>
       <c r="E22" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>15</v>
@@ -1798,19 +1848,20 @@
       <c r="I22" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="2"/>
+      <c r="K22" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K22" s="2">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="L22" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B23" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>59</v>
@@ -1833,19 +1884,20 @@
       <c r="I23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J23" s="2"/>
+      <c r="K23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K23" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="L23" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B24" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>59</v>
@@ -1868,19 +1920,20 @@
       <c r="I24" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="2"/>
+      <c r="K24" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K24" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="L24" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B25" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>59</v>
@@ -1903,19 +1956,20 @@
       <c r="I25" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="2"/>
+      <c r="K25" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K25" s="2">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="26" ht="18.0" customHeight="1">
+      <c r="L25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B26" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>59</v>
@@ -1924,7 +1978,7 @@
         <v>13</v>
       </c>
       <c r="E26" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>15</v>
@@ -1938,19 +1992,20 @@
       <c r="I26" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J26" s="2"/>
+      <c r="K26" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K26" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="L26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B27" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>59</v>
@@ -1973,19 +2028,20 @@
       <c r="I27" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="J27" s="2"/>
+      <c r="K27" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K27" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="L27" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>59</v>
@@ -1994,7 +2050,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>15</v>
@@ -2008,19 +2064,20 @@
       <c r="I28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J28" s="2"/>
+      <c r="K28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K28" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="L28" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B29" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>59</v>
@@ -2043,19 +2100,20 @@
       <c r="I29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="J29" s="2"/>
+      <c r="K29" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K29" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="30">
+      <c r="L29" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B30" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>59</v>
@@ -2078,19 +2136,20 @@
       <c r="I30" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="J30" s="2"/>
+      <c r="K30" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K30" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="31">
+      <c r="L30" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B31" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>59</v>
@@ -2099,7 +2158,7 @@
         <v>13</v>
       </c>
       <c r="E31" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>15</v>
@@ -2113,19 +2172,20 @@
       <c r="I31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="J31" s="2"/>
+      <c r="K31" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K31" s="2">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="L31" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B32" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>59</v>
@@ -2134,7 +2194,7 @@
         <v>13</v>
       </c>
       <c r="E32" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>15</v>
@@ -2148,19 +2208,20 @@
       <c r="I32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="J32" s="2"/>
+      <c r="K32" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K32" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="L32" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B33" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>59</v>
@@ -2169,7 +2230,7 @@
         <v>13</v>
       </c>
       <c r="E33" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>15</v>
@@ -2183,19 +2244,20 @@
       <c r="I33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="J33" s="2"/>
+      <c r="K33" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K33" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="34">
+      <c r="L33" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B34" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>12</v>
@@ -2218,19 +2280,20 @@
       <c r="I34" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="J34" s="2"/>
+      <c r="K34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K34" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="35">
+      <c r="L34" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B35" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>12</v>
@@ -2239,7 +2302,7 @@
         <v>13</v>
       </c>
       <c r="E35" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>15</v>
@@ -2253,19 +2316,20 @@
       <c r="I35" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="J35" s="2"/>
+      <c r="K35" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="2">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="36">
+      <c r="L35" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B36" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>12</v>
@@ -2288,19 +2352,20 @@
       <c r="I36" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="J36" s="2"/>
+      <c r="K36" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K36" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="37">
+      <c r="L36" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B37" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>12</v>
@@ -2309,7 +2374,7 @@
         <v>13</v>
       </c>
       <c r="E37" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>15</v>
@@ -2323,19 +2388,20 @@
       <c r="I37" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="J37" s="2"/>
+      <c r="K37" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K37" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="L37" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B38" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>12</v>
@@ -2358,19 +2424,20 @@
       <c r="I38" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="J38" s="2"/>
+      <c r="K38" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K38" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="39">
+      <c r="L38" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B39" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>12</v>
@@ -2379,7 +2446,7 @@
         <v>13</v>
       </c>
       <c r="E39" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>15</v>
@@ -2393,19 +2460,20 @@
       <c r="I39" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J39" s="2" t="s">
+      <c r="J39" s="2"/>
+      <c r="K39" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K39" s="2">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="40">
+      <c r="L39" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B40" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>12</v>
@@ -2414,7 +2482,7 @@
         <v>13</v>
       </c>
       <c r="E40" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>15</v>
@@ -2428,19 +2496,20 @@
       <c r="I40" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="J40" s="2" t="s">
+      <c r="J40" s="2"/>
+      <c r="K40" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K40" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="41">
+      <c r="L40" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B41" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>12</v>
@@ -2463,19 +2532,20 @@
       <c r="I41" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="J41" s="2"/>
+      <c r="K41" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K41" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="42">
+      <c r="L41" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B42" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>12</v>
@@ -2498,19 +2568,20 @@
       <c r="I42" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="J42" s="2" t="s">
+      <c r="J42" s="2"/>
+      <c r="K42" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K42" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="43">
+      <c r="L42" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B43" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>12</v>
@@ -2533,19 +2604,20 @@
       <c r="I43" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J43" s="2" t="s">
+      <c r="J43" s="2"/>
+      <c r="K43" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K43" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="44">
+      <c r="L43" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B44" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>12</v>
@@ -2568,19 +2640,20 @@
       <c r="I44" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J44" s="2" t="s">
+      <c r="J44" s="2"/>
+      <c r="K44" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K44" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="45">
+      <c r="L44" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B45" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>12</v>
@@ -2603,19 +2676,20 @@
       <c r="I45" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="J45" s="2" t="s">
+      <c r="J45" s="2"/>
+      <c r="K45" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K45" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="46">
+      <c r="L45" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B46" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>12</v>
@@ -2638,93 +2712,96 @@
       <c r="I46" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="J46" s="2" t="s">
+      <c r="J46" s="2"/>
+      <c r="K46" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K46" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="s">
+      <c r="L46" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B47" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C47" s="6" t="s">
+      <c r="B47" s="4">
+        <v>5</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F47" s="6" t="s">
+      <c r="D47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G47" s="6" t="s">
+      <c r="G47" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6" t="s">
+      <c r="H47" s="4"/>
+      <c r="I47" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="J47" s="6" t="s">
+      <c r="J47" s="4"/>
+      <c r="K47" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K47" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="7"/>
-    </row>
-    <row r="48" ht="18.0" customHeight="1">
-      <c r="A48" s="6" t="s">
+      <c r="L47" s="4">
+        <v>3</v>
+      </c>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+    </row>
+    <row r="48" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C48" s="6" t="s">
+      <c r="B48" s="4">
+        <v>5</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G48" s="6" t="s">
+      <c r="D48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="4">
+        <v>4</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="H48" s="6" t="s">
+      <c r="H48" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="I48" s="6" t="s">
+      <c r="I48" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J48" s="6" t="s">
+      <c r="J48" s="4"/>
+      <c r="K48" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K48" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
-    </row>
-    <row r="49">
+      <c r="L48" s="4">
+        <v>2</v>
+      </c>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+    </row>
+    <row r="49" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B49" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>42</v>
@@ -2747,19 +2824,20 @@
       <c r="I49" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="J49" s="2"/>
+      <c r="K49" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K49" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="50" ht="18.0" customHeight="1">
+      <c r="L49" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B50" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>42</v>
@@ -2768,7 +2846,7 @@
         <v>13</v>
       </c>
       <c r="E50" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>15</v>
@@ -2782,19 +2860,20 @@
       <c r="I50" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J50" s="2" t="s">
+      <c r="J50" s="2"/>
+      <c r="K50" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K50" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="51">
+      <c r="L50" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B51" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>42</v>
@@ -2803,7 +2882,7 @@
         <v>13</v>
       </c>
       <c r="E51" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>15</v>
@@ -2817,476 +2896,486 @@
       <c r="I51" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="J51" s="2"/>
+      <c r="K51" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K51" s="2">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="s">
+      <c r="L51" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B52" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C52" s="6" t="s">
+      <c r="B52" s="4">
+        <v>5</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F52" s="6" t="s">
+      <c r="D52" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="G52" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H52" s="6" t="s">
+      <c r="H52" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I52" s="6" t="s">
+      <c r="I52" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J52" s="6" t="s">
+      <c r="J52" s="4"/>
+      <c r="K52" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K52" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-      <c r="O52" s="7"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="7"/>
-      <c r="R52" s="7"/>
-      <c r="S52" s="7"/>
-      <c r="T52" s="7"/>
-      <c r="U52" s="7"/>
-      <c r="V52" s="7"/>
-      <c r="W52" s="7"/>
-      <c r="X52" s="7"/>
-      <c r="Y52" s="7"/>
-      <c r="Z52" s="7"/>
-      <c r="AA52" s="7"/>
-    </row>
-    <row r="53" ht="18.0" customHeight="1">
-      <c r="A53" s="6" t="s">
+      <c r="L52" s="4">
+        <v>3</v>
+      </c>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="4"/>
+      <c r="V52" s="4"/>
+      <c r="W52" s="4"/>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="4"/>
+      <c r="AB52" s="4"/>
+    </row>
+    <row r="53" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B53" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C53" s="6" t="s">
+      <c r="B53" s="4">
+        <v>5</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="F53" s="6" t="s">
+      <c r="D53" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="4">
+        <v>3</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G53" s="6" t="s">
+      <c r="G53" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H53" s="6" t="s">
+      <c r="H53" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="I53" s="6" t="s">
+      <c r="I53" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="J53" s="6" t="s">
+      <c r="J53" s="4"/>
+      <c r="K53" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K53" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="7"/>
-      <c r="O53" s="7"/>
-      <c r="P53" s="7"/>
-      <c r="Q53" s="7"/>
-      <c r="R53" s="7"/>
-      <c r="S53" s="7"/>
-      <c r="T53" s="7"/>
-      <c r="U53" s="7"/>
-      <c r="V53" s="7"/>
-      <c r="W53" s="7"/>
-      <c r="X53" s="7"/>
-      <c r="Y53" s="7"/>
-      <c r="Z53" s="7"/>
-      <c r="AA53" s="7"/>
-    </row>
-    <row r="54" ht="17.25" customHeight="1">
-      <c r="A54" s="6" t="s">
+      <c r="L53" s="4">
+        <v>2</v>
+      </c>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4"/>
+      <c r="V53" s="4"/>
+      <c r="W53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
+      <c r="AB53" s="4"/>
+    </row>
+    <row r="54" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B54" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C54" s="6" t="s">
+      <c r="B54" s="4">
+        <v>5</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="6" t="s">
+      <c r="D54" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="G54" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H54" s="6" t="s">
+      <c r="H54" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="I54" s="6" t="s">
+      <c r="I54" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J54" s="6" t="s">
+      <c r="J54" s="4"/>
+      <c r="K54" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K54" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="7"/>
-      <c r="O54" s="7"/>
-      <c r="P54" s="7"/>
-      <c r="Q54" s="7"/>
-      <c r="R54" s="7"/>
-      <c r="S54" s="7"/>
-      <c r="T54" s="7"/>
-      <c r="U54" s="7"/>
-      <c r="V54" s="7"/>
-      <c r="W54" s="7"/>
-      <c r="X54" s="7"/>
-      <c r="Y54" s="7"/>
-      <c r="Z54" s="7"/>
-      <c r="AA54" s="7"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="s">
+      <c r="L54" s="4">
+        <v>3</v>
+      </c>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="4"/>
+      <c r="AB54" s="4"/>
+    </row>
+    <row r="55" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B55" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C55" s="6" t="s">
+      <c r="B55" s="4">
+        <v>5</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F55" s="6" t="s">
+      <c r="D55" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="4">
+        <v>1</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G55" s="6" t="s">
+      <c r="G55" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H55" s="6" t="s">
+      <c r="H55" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="I55" s="6" t="s">
+      <c r="I55" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="J55" s="6" t="s">
+      <c r="J55" s="4"/>
+      <c r="K55" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K55" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="7"/>
-      <c r="O55" s="7"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="7"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="7"/>
-      <c r="T55" s="7"/>
-      <c r="U55" s="7"/>
-      <c r="V55" s="7"/>
-      <c r="W55" s="7"/>
-      <c r="X55" s="7"/>
-      <c r="Y55" s="7"/>
-      <c r="Z55" s="7"/>
-      <c r="AA55" s="7"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="s">
+      <c r="L55" s="4">
+        <v>2</v>
+      </c>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+      <c r="AA55" s="4"/>
+      <c r="AB55" s="4"/>
+    </row>
+    <row r="56" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B56" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C56" s="6" t="s">
+      <c r="B56" s="4">
+        <v>5</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="D56" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="H56" s="6" t="s">
+      <c r="H56" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="I56" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J56" s="6" t="s">
+      <c r="J56" s="4"/>
+      <c r="K56" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K56" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="L56" s="7"/>
-      <c r="M56" s="7"/>
-      <c r="N56" s="7"/>
-      <c r="O56" s="7"/>
-      <c r="P56" s="7"/>
-      <c r="Q56" s="7"/>
-      <c r="R56" s="7"/>
-      <c r="S56" s="7"/>
-      <c r="T56" s="7"/>
-      <c r="U56" s="7"/>
-      <c r="V56" s="7"/>
-      <c r="W56" s="7"/>
-      <c r="X56" s="7"/>
-      <c r="Y56" s="7"/>
-      <c r="Z56" s="7"/>
-      <c r="AA56" s="7"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="s">
+      <c r="L56" s="4">
+        <v>3</v>
+      </c>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="4"/>
+      <c r="AB56" s="4"/>
+    </row>
+    <row r="57" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B57" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C57" s="6" t="s">
+      <c r="B57" s="4">
+        <v>5</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" s="6" t="s">
+      <c r="D57" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="H57" s="6" t="s">
+      <c r="H57" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="I57" s="6" t="s">
+      <c r="I57" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J57" s="6" t="s">
+      <c r="J57" s="4"/>
+      <c r="K57" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K57" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="L57" s="7"/>
-      <c r="M57" s="7"/>
-      <c r="N57" s="7"/>
-      <c r="O57" s="7"/>
-      <c r="P57" s="7"/>
-      <c r="Q57" s="7"/>
-      <c r="R57" s="7"/>
-      <c r="S57" s="7"/>
-      <c r="T57" s="7"/>
-      <c r="U57" s="7"/>
-      <c r="V57" s="7"/>
-      <c r="W57" s="7"/>
-      <c r="X57" s="7"/>
-      <c r="Y57" s="7"/>
-      <c r="Z57" s="7"/>
-      <c r="AA57" s="7"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="s">
+      <c r="L57" s="4">
+        <v>3</v>
+      </c>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="4"/>
+      <c r="AB57" s="4"/>
+    </row>
+    <row r="58" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B58" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C58" s="6" t="s">
+      <c r="B58" s="4">
+        <v>5</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G58" s="6" t="s">
+      <c r="D58" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="4">
+        <v>4</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="H58" s="6" t="s">
+      <c r="H58" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="I58" s="6" t="s">
+      <c r="I58" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J58" s="6" t="s">
+      <c r="J58" s="4"/>
+      <c r="K58" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K58" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="L58" s="7"/>
-      <c r="M58" s="7"/>
-      <c r="N58" s="7"/>
-      <c r="O58" s="7"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="7"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="7"/>
-      <c r="T58" s="7"/>
-      <c r="U58" s="7"/>
-      <c r="V58" s="7"/>
-      <c r="W58" s="7"/>
-      <c r="X58" s="7"/>
-      <c r="Y58" s="7"/>
-      <c r="Z58" s="7"/>
-      <c r="AA58" s="7"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="s">
+      <c r="L58" s="4">
+        <v>1</v>
+      </c>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="U58" s="4"/>
+      <c r="V58" s="4"/>
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="4"/>
+      <c r="AA58" s="4"/>
+      <c r="AB58" s="4"/>
+    </row>
+    <row r="59" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B59" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C59" s="6" t="s">
+      <c r="B59" s="4">
+        <v>5</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G59" s="6" t="s">
+      <c r="D59" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="4">
+        <v>4</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="H59" s="6" t="s">
+      <c r="H59" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I59" s="6" t="s">
+      <c r="I59" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J59" s="6" t="s">
+      <c r="J59" s="4"/>
+      <c r="K59" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K59" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="L59" s="7"/>
-      <c r="M59" s="7"/>
-      <c r="N59" s="7"/>
-      <c r="O59" s="7"/>
-      <c r="P59" s="7"/>
-      <c r="Q59" s="7"/>
-      <c r="R59" s="7"/>
-      <c r="S59" s="7"/>
-      <c r="T59" s="7"/>
-      <c r="U59" s="7"/>
-      <c r="V59" s="7"/>
-      <c r="W59" s="7"/>
-      <c r="X59" s="7"/>
-      <c r="Y59" s="7"/>
-      <c r="Z59" s="7"/>
-      <c r="AA59" s="7"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="s">
+      <c r="L59" s="4">
+        <v>4</v>
+      </c>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
+      <c r="U59" s="4"/>
+      <c r="V59" s="4"/>
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+      <c r="AA59" s="4"/>
+      <c r="AB59" s="4"/>
+    </row>
+    <row r="60" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B60" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C60" s="6" t="s">
+      <c r="B60" s="4">
+        <v>5</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F60" s="6" t="s">
+      <c r="D60" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G60" s="6" t="s">
+      <c r="G60" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6" t="s">
+      <c r="H60" s="4"/>
+      <c r="I60" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="J60" s="6" t="s">
+      <c r="J60" s="4"/>
+      <c r="K60" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K60" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="L60" s="7"/>
-      <c r="M60" s="7"/>
-      <c r="N60" s="7"/>
-      <c r="O60" s="7"/>
-      <c r="P60" s="7"/>
-      <c r="Q60" s="7"/>
-      <c r="R60" s="7"/>
-      <c r="S60" s="7"/>
-      <c r="T60" s="7"/>
-      <c r="U60" s="7"/>
-      <c r="V60" s="7"/>
-      <c r="W60" s="7"/>
-      <c r="X60" s="7"/>
-      <c r="Y60" s="7"/>
-      <c r="Z60" s="7"/>
-      <c r="AA60" s="7"/>
-    </row>
-    <row r="61">
+      <c r="L60" s="4">
+        <v>3</v>
+      </c>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="S60" s="4"/>
+      <c r="T60" s="4"/>
+      <c r="U60" s="4"/>
+      <c r="V60" s="4"/>
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+      <c r="AA60" s="4"/>
+      <c r="AB60" s="4"/>
+    </row>
+    <row r="61" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B61" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>59</v>
@@ -3297,7 +3386,7 @@
       <c r="E61" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F61" s="6" t="s">
+      <c r="F61" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G61" s="2" t="s">
@@ -3309,19 +3398,20 @@
       <c r="I61" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J61" s="2" t="s">
+      <c r="J61" s="2"/>
+      <c r="K61" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K61" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="62">
+      <c r="L61" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B62" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>59</v>
@@ -3330,9 +3420,9 @@
         <v>13</v>
       </c>
       <c r="E62" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="F62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G62" s="2" t="s">
@@ -3344,19 +3434,20 @@
       <c r="I62" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="J62" s="2" t="s">
+      <c r="J62" s="2"/>
+      <c r="K62" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K62" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="63">
+      <c r="L62" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B63" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>59</v>
@@ -3367,7 +3458,7 @@
       <c r="E63" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F63" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G63" s="2" t="s">
@@ -3379,19 +3470,20 @@
       <c r="I63" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J63" s="2" t="s">
+      <c r="J63" s="2"/>
+      <c r="K63" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K63" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="64">
+      <c r="L63" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B64" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>59</v>
@@ -3400,9 +3492,9 @@
         <v>13</v>
       </c>
       <c r="E64" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="F64" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G64" s="2" t="s">
@@ -3414,19 +3506,20 @@
       <c r="I64" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J64" s="2" t="s">
+      <c r="J64" s="2"/>
+      <c r="K64" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K64" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="65">
+      <c r="L64" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B65" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>59</v>
@@ -3437,7 +3530,7 @@
       <c r="E65" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="F65" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G65" s="2" t="s">
@@ -3449,19 +3542,20 @@
       <c r="I65" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J65" s="2" t="s">
+      <c r="J65" s="2"/>
+      <c r="K65" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K65" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="66">
+      <c r="L65" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B66" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>59</v>
@@ -3470,9 +3564,9 @@
         <v>13</v>
       </c>
       <c r="E66" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="F66" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G66" s="2" t="s">
@@ -3484,19 +3578,20 @@
       <c r="I66" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J66" s="2" t="s">
+      <c r="J66" s="2"/>
+      <c r="K66" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K66" s="2">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="67">
+      <c r="L66" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B67" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>59</v>
@@ -3505,9 +3600,9 @@
         <v>13</v>
       </c>
       <c r="E67" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="F67" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F67" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G67" s="2" t="s">
@@ -3519,19 +3614,20 @@
       <c r="I67" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="J67" s="2" t="s">
+      <c r="J67" s="2"/>
+      <c r="K67" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K67" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="68">
+      <c r="L67" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B68" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>59</v>
@@ -3554,19 +3650,20 @@
       <c r="I68" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J68" s="2" t="s">
+      <c r="J68" s="2"/>
+      <c r="K68" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K68" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="69">
+      <c r="L68" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B69" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>59</v>
@@ -3575,7 +3672,7 @@
         <v>13</v>
       </c>
       <c r="E69" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>15</v>
@@ -3589,19 +3686,20 @@
       <c r="I69" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J69" s="2" t="s">
+      <c r="J69" s="2"/>
+      <c r="K69" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K69" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="70">
+      <c r="L69" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B70" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>59</v>
@@ -3622,19 +3720,20 @@
       <c r="I70" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="J70" s="2" t="s">
+      <c r="J70" s="2"/>
+      <c r="K70" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K70" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="71">
+      <c r="L70" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B71" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>12</v>
@@ -3657,19 +3756,20 @@
       <c r="I71" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J71" s="2" t="s">
+      <c r="J71" s="2"/>
+      <c r="K71" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K71" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="72">
+      <c r="L71" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B72" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>12</v>
@@ -3678,7 +3778,7 @@
         <v>13</v>
       </c>
       <c r="E72" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>15</v>
@@ -3692,19 +3792,20 @@
       <c r="I72" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="J72" s="2" t="s">
+      <c r="J72" s="2"/>
+      <c r="K72" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K72" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="73">
+      <c r="L72" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B73" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>12</v>
@@ -3727,19 +3828,20 @@
       <c r="I73" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J73" s="2" t="s">
+      <c r="J73" s="2"/>
+      <c r="K73" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K73" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="74">
+      <c r="L73" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B74" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>12</v>
@@ -3748,7 +3850,7 @@
         <v>13</v>
       </c>
       <c r="E74" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>143</v>
@@ -3762,19 +3864,20 @@
       <c r="I74" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="J74" s="2" t="s">
+      <c r="J74" s="2"/>
+      <c r="K74" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K74" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="75">
+      <c r="L74" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B75" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>12</v>
@@ -3797,19 +3900,20 @@
       <c r="I75" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J75" s="2" t="s">
+      <c r="J75" s="2"/>
+      <c r="K75" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K75" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="76">
+      <c r="L75" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B76" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>12</v>
@@ -3818,7 +3922,7 @@
         <v>13</v>
       </c>
       <c r="E76" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>143</v>
@@ -3832,19 +3936,20 @@
       <c r="I76" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="J76" s="2" t="s">
+      <c r="J76" s="2"/>
+      <c r="K76" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K76" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="77">
+      <c r="L76" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B77" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>12</v>
@@ -3867,19 +3972,20 @@
       <c r="I77" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J77" s="2" t="s">
+      <c r="J77" s="2"/>
+      <c r="K77" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K77" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="78">
+      <c r="L77" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B78" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>12</v>
@@ -3888,7 +3994,7 @@
         <v>13</v>
       </c>
       <c r="E78" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>143</v>
@@ -3902,19 +4008,20 @@
       <c r="I78" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J78" s="2" t="s">
+      <c r="J78" s="2"/>
+      <c r="K78" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K78" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="79">
+      <c r="L78" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B79" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>12</v>
@@ -3937,19 +4044,20 @@
       <c r="I79" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J79" s="2" t="s">
+      <c r="J79" s="2"/>
+      <c r="K79" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K79" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="80">
+      <c r="L79" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B80" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>12</v>
@@ -3958,7 +4066,7 @@
         <v>13</v>
       </c>
       <c r="E80" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>149</v>
@@ -3972,19 +4080,20 @@
       <c r="I80" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="J80" s="2" t="s">
+      <c r="J80" s="2"/>
+      <c r="K80" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K80" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="81">
+      <c r="L80" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B81" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>12</v>
@@ -4007,19 +4116,20 @@
       <c r="I81" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J81" s="2" t="s">
+      <c r="J81" s="2"/>
+      <c r="K81" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K81" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="82">
+      <c r="L81" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B82" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>12</v>
@@ -4028,7 +4138,7 @@
         <v>13</v>
       </c>
       <c r="E82" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>149</v>
@@ -4042,19 +4152,20 @@
       <c r="I82" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J82" s="2" t="s">
+      <c r="J82" s="2"/>
+      <c r="K82" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K82" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="83">
+      <c r="L82" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B83" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>12</v>
@@ -4077,19 +4188,20 @@
       <c r="I83" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J83" s="2" t="s">
+      <c r="J83" s="2"/>
+      <c r="K83" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K83" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="84">
+      <c r="L83" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B84" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>12</v>
@@ -4098,7 +4210,7 @@
         <v>13</v>
       </c>
       <c r="E84" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>149</v>
@@ -4112,19 +4224,20 @@
       <c r="I84" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J84" s="2" t="s">
+      <c r="J84" s="2"/>
+      <c r="K84" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K84" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="85">
+      <c r="L84" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B85" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>12</v>
@@ -4144,19 +4257,20 @@
       <c r="I85" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="J85" s="2" t="s">
+      <c r="J85" s="2"/>
+      <c r="K85" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K85" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="86">
+      <c r="L85" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B86" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>12</v>
@@ -4176,19 +4290,20 @@
       <c r="I86" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="J86" s="2" t="s">
+      <c r="J86" s="2"/>
+      <c r="K86" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K86" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="87">
+      <c r="L86" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B87" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>14</v>
@@ -4211,19 +4326,20 @@
       <c r="I87" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J87" s="2" t="s">
+      <c r="J87" s="2"/>
+      <c r="K87" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K87" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="88">
+      <c r="L87" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B88" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>14</v>
@@ -4232,7 +4348,7 @@
         <v>13</v>
       </c>
       <c r="E88" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>157</v>
@@ -4246,19 +4362,20 @@
       <c r="I88" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J88" s="2" t="s">
+      <c r="J88" s="2"/>
+      <c r="K88" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K88" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="89">
+      <c r="L88" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B89" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>14</v>
@@ -4281,19 +4398,20 @@
       <c r="I89" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J89" s="2" t="s">
+      <c r="J89" s="2"/>
+      <c r="K89" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K89" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="90">
+      <c r="L89" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B90" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>14</v>
@@ -4302,7 +4420,7 @@
         <v>13</v>
       </c>
       <c r="E90" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>157</v>
@@ -4316,19 +4434,20 @@
       <c r="I90" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J90" s="2" t="s">
+      <c r="J90" s="2"/>
+      <c r="K90" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K90" s="2">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="91">
+      <c r="L90" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B91" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>14</v>
@@ -4351,19 +4470,20 @@
       <c r="I91" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J91" s="2" t="s">
+      <c r="J91" s="2"/>
+      <c r="K91" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K91" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="92">
+      <c r="L91" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B92" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>14</v>
@@ -4386,19 +4506,20 @@
       <c r="I92" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J92" s="2" t="s">
+      <c r="J92" s="2"/>
+      <c r="K92" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K92" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="93">
+      <c r="L92" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B93" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>14</v>
@@ -4407,7 +4528,7 @@
         <v>13</v>
       </c>
       <c r="E93" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>157</v>
@@ -4421,19 +4542,20 @@
       <c r="I93" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J93" s="2" t="s">
+      <c r="J93" s="2"/>
+      <c r="K93" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K93" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="94">
+      <c r="L93" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B94" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>14</v>
@@ -4456,19 +4578,20 @@
       <c r="I94" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J94" s="2" t="s">
+      <c r="J94" s="2"/>
+      <c r="K94" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K94" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="95">
+      <c r="L94" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B95" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>14</v>
@@ -4491,19 +4614,20 @@
       <c r="I95" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J95" s="2" t="s">
+      <c r="J95" s="2"/>
+      <c r="K95" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K95" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="96">
+      <c r="L95" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B96" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>14</v>
@@ -4512,7 +4636,7 @@
         <v>13</v>
       </c>
       <c r="E96" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>157</v>
@@ -4526,19 +4650,20 @@
       <c r="I96" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J96" s="2" t="s">
+      <c r="J96" s="2"/>
+      <c r="K96" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K96" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="97">
+      <c r="L96" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B97" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>14</v>
@@ -4561,19 +4686,20 @@
       <c r="I97" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J97" s="2" t="s">
+      <c r="J97" s="2"/>
+      <c r="K97" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K97" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="98">
+      <c r="L97" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B98" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>14</v>
@@ -4596,19 +4722,20 @@
       <c r="I98" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J98" s="2" t="s">
+      <c r="J98" s="2"/>
+      <c r="K98" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K98" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="99">
+      <c r="L98" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B99" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>14</v>
@@ -4631,19 +4758,20 @@
       <c r="I99" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J99" s="2" t="s">
+      <c r="J99" s="2"/>
+      <c r="K99" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K99" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="100">
+      <c r="L99" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B100" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>14</v>
@@ -4666,26 +4794,28 @@
       <c r="I100" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J100" s="2" t="s">
+      <c r="J100" s="2"/>
+      <c r="K100" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K100" s="2">
-        <v>3.0</v>
+      <c r="L100" s="2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -4693,7 +4823,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>45</v>
       </c>
@@ -4701,7 +4831,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>62</v>
       </c>
@@ -4709,7 +4839,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
@@ -4717,7 +4847,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>108</v>
       </c>
@@ -4725,7 +4855,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>80</v>
       </c>
@@ -4733,7 +4863,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>141</v>
       </c>
@@ -4741,7 +4871,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>124</v>
       </c>
@@ -4749,7 +4879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>174</v>
       </c>
@@ -4757,7 +4887,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>175</v>
       </c>
@@ -4765,751 +4895,784 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>176</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>89</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="B16" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>92</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>85</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:L23"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="15.5"/>
-    <col customWidth="1" min="3" max="3" width="10.38"/>
-    <col customWidth="1" min="4" max="4" width="7.88"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="8"/>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3">
+    <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="7">
+        <v>3</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E4" s="9">
+        <v>46304</v>
+      </c>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="7">
+        <v>3</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E5" s="9">
+        <v>46336</v>
+      </c>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="7">
+        <v>3</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="9">
+        <v>46304</v>
+      </c>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C7" s="7">
+        <v>3</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="F3" s="9"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="s">
+      <c r="E7" s="9">
+        <v>46146</v>
+      </c>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B8" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="D4" s="17" t="s">
+      <c r="C8" s="7">
+        <v>3</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="9">
+        <v>46178</v>
+      </c>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="7">
+        <v>3</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" s="9">
+        <v>46146</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="9">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E4" s="18">
-        <v>46304.0</v>
-      </c>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="D5" s="17" t="s">
+      <c r="C10" s="7">
+        <v>5</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="9">
+        <v>46304</v>
+      </c>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E5" s="18">
-        <v>46336.0</v>
-      </c>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="C6" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="D6" s="17" t="s">
+      <c r="C11" s="7">
+        <v>5</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="E11" s="9">
+        <v>46304</v>
+      </c>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="7">
+        <v>5</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="9">
+        <v>46304</v>
+      </c>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="11">
+        <v>5</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E13" s="9">
+        <v>46335</v>
+      </c>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="7">
+        <v>5</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="18">
-        <v>46304.0</v>
-      </c>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="C7" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="E14" s="9">
+        <v>46335</v>
+      </c>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="11">
+        <v>7</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="9">
+        <v>46304</v>
+      </c>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="11">
+        <v>7</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E16" s="9">
+        <v>46304</v>
+      </c>
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="11">
+        <v>7</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="E7" s="18">
-        <v>46146.0</v>
-      </c>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="C8" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="D8" s="19" t="s">
+      <c r="E17" s="9">
+        <v>46304</v>
+      </c>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" s="11">
+        <v>7</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" s="9">
+        <v>46336</v>
+      </c>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C19" s="11">
+        <v>7</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="E19" s="9">
+        <v>46336</v>
+      </c>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="11">
+        <v>7</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="E8" s="18">
-        <v>46178.0</v>
-      </c>
-      <c r="F8" s="9"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="C9" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="E9" s="18">
-        <v>46146.0</v>
-      </c>
-      <c r="F9" s="9"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="18">
-        <v>46146.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="16" t="s">
+      <c r="E20" s="9">
+        <v>46336</v>
+      </c>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C10" s="15">
-        <v>5.0</v>
-      </c>
-      <c r="D10" s="17" t="s">
+      <c r="C21" s="11">
+        <v>7</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="9">
+        <v>46335</v>
+      </c>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" s="11">
+        <v>7</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E22" s="9">
+        <v>46177</v>
+      </c>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D23" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E10" s="18">
-        <v>46304.0</v>
-      </c>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C11" s="15">
-        <v>5.0</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="E11" s="18">
-        <v>46304.0</v>
-      </c>
-      <c r="F11" s="9"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C12" s="15">
-        <v>5.0</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="E12" s="18">
-        <v>46304.0</v>
-      </c>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C13" s="20">
-        <v>5.0</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="E13" s="18">
-        <v>46335.0</v>
-      </c>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C14" s="15">
-        <v>5.0</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="18">
-        <v>46335.0</v>
-      </c>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="20">
-        <v>7.0</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="E15" s="18">
-        <v>46304.0</v>
-      </c>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="20">
-        <v>7.0</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="E16" s="18">
-        <v>46304.0</v>
-      </c>
-      <c r="F16" s="9"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" s="20">
-        <v>7.0</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="E17" s="18">
-        <v>46304.0</v>
-      </c>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C18" s="20">
-        <v>7.0</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="E18" s="18">
-        <v>46336.0</v>
-      </c>
-      <c r="F18" s="9"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C19" s="20">
-        <v>7.0</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="E19" s="18">
-        <v>46336.0</v>
-      </c>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C20" s="20">
-        <v>7.0</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="E20" s="18">
-        <v>46336.0</v>
-      </c>
-      <c r="F20" s="9"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C21" s="20">
-        <v>7.0</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="18">
-        <v>46335.0</v>
-      </c>
-      <c r="F21" s="9"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C22" s="20">
-        <v>7.0</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="E22" s="18">
-        <v>46177.0</v>
-      </c>
-      <c r="F22" s="9"/>
-    </row>
-    <row r="23">
-      <c r="D23" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.25"/>
-    <col customWidth="1" min="2" max="2" width="7.25"/>
+    <col min="1" max="1" width="14.21875" customWidth="1"/>
+    <col min="2" max="2" width="7.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>186</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="22">
-        <v>46034.0</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="C2" s="12">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="22">
-        <v>46114.0</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3" s="12">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="12">
+        <v>46114</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C4" s="22">
-        <v>46114.0</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="12">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="22">
-        <v>46114.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6" s="22">
-        <v>46367.0</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="C6" s="12">
+        <v>46367</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C7" s="22">
-        <v>46033.0</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="C7" s="12">
+        <v>46033</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="22">
-        <v>46083.0</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="C8" s="12">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C9" s="22">
-        <v>46304.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>183</v>
+      </c>
+      <c r="C9" s="12">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C10" s="22">
-        <v>46033.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>183</v>
+      </c>
+      <c r="C10" s="12">
+        <v>46033</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C11" s="22">
-        <v>46033.0</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>182</v>
+      </c>
+      <c r="C11" s="12">
+        <v>46033</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>154</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C12" s="22">
-        <v>46367.0</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>183</v>
+      </c>
+      <c r="C12" s="12">
+        <v>46367</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>154</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C13" s="22">
-        <v>46367.0</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>182</v>
+      </c>
+      <c r="C13" s="12">
+        <v>46367</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>154</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C14" s="22">
-        <v>46335.0</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>181</v>
+      </c>
+      <c r="C14" s="12">
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C15" s="22">
-        <v>46114.0</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="C15" s="12">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C16" s="22">
-        <v>46114.0</v>
+        <v>182</v>
+      </c>
+      <c r="C16" s="12">
+        <v>46114</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
-  <drawing r:id="rId1"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>